--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1404,7 +1404,7 @@
     <t>Patient.extension:identityReliability.extension:identityStatus.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-reliability-ins-status|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-reliability|2.2.0</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:comment</t>
@@ -1428,7 +1428,7 @@
     <t>Patient.extension:identityReliability.extension:comment.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-reliability|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/git|2.2.0</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:validationDate</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1428,7 +1428,7 @@
     <t>Patient.extension:identityReliability.extension:comment.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/git|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-reliability-supplement|2.2.0</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:validationDate</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1404,7 +1404,7 @@
     <t>Patient.extension:identityReliability.extension:identityStatus.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-reliability|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-status|2.2.0</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:comment</t>
@@ -1428,7 +1428,7 @@
     <t>Patient.extension:identityReliability.extension:comment.value[x]</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-reliability-supplement|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-status-comment|2.2.0</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:validationDate</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9781" uniqueCount="1047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9781" uniqueCount="1048">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1328,7 +1328,10 @@
     <t>methodCollection</t>
   </si>
   <si>
-    <t>The way the INS identity is collected | Mode d'obtention de l'INS (SM, CV, INSI, ...)</t>
+    <t>Channel used to collect the identity traits or the INS | Canal d'obtention des traits d'identité ou de l'INS (SM, CV, INSi, CB, RFID, AV)</t>
+  </si>
+  <si>
+    <t>Précise le canal technique par lequel les traits d'identité ou l'INS ont été obtenus (RNIV §4.3) : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:methodCollection.id</t>
@@ -10698,7 +10701,7 @@
         <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>199</v>
+        <v>421</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10781,10 +10784,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10896,10 +10899,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11011,10 +11014,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11128,10 +11131,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11160,7 +11163,7 @@
         <v>221</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -11191,7 +11194,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -11241,13 +11244,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>82</v>
@@ -11272,10 +11275,10 @@
         <v>111</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11358,10 +11361,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11473,10 +11476,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11588,10 +11591,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11631,7 +11634,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>82</v>
@@ -11705,10 +11708,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11731,13 +11734,13 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>221</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11820,13 +11823,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>82</v>
@@ -11937,10 +11940,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12052,10 +12055,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12167,10 +12170,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12210,7 +12213,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>82</v>
@@ -12284,10 +12287,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12316,7 +12319,7 @@
         <v>221</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -12347,7 +12350,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -12397,13 +12400,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>82</v>
@@ -12428,7 +12431,7 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>199</v>
@@ -12514,10 +12517,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12629,10 +12632,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12744,10 +12747,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12787,7 +12790,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>82</v>
@@ -12861,10 +12864,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12893,7 +12896,7 @@
         <v>221</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12924,7 +12927,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12974,13 +12977,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>82</v>
@@ -13005,7 +13008,7 @@
         <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>199</v>
@@ -13091,10 +13094,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13206,10 +13209,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13321,10 +13324,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13364,7 +13367,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>82</v>
@@ -13438,10 +13441,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13464,13 +13467,13 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>221</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13553,13 +13556,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
@@ -13670,10 +13673,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13785,10 +13788,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13900,10 +13903,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13943,7 +13946,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>82</v>
@@ -14017,10 +14020,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14049,7 +14052,7 @@
         <v>221</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -14080,7 +14083,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -14130,7 +14133,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>212</v>
@@ -14173,7 +14176,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -14247,7 +14250,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>219</v>
@@ -14273,13 +14276,13 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>221</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -14362,13 +14365,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>82</v>
@@ -14390,13 +14393,13 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14479,13 +14482,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>82</v>
@@ -14507,13 +14510,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14596,10 +14599,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14625,16 +14628,16 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14683,7 +14686,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14715,10 +14718,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14741,17 +14744,17 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14788,10 +14791,10 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
@@ -14800,7 +14803,7 @@
         <v>117</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14815,16 +14818,16 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14832,13 +14835,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>82</v>
@@ -14860,17 +14863,17 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14919,7 +14922,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14934,16 +14937,16 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14951,10 +14954,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15066,10 +15069,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15183,10 +15186,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15212,16 +15215,16 @@
         <v>173</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15231,7 +15234,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -15249,10 +15252,10 @@
         <v>241</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -15270,7 +15273,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15285,7 +15288,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -15302,10 +15305,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15328,19 +15331,19 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -15350,7 +15353,7 @@
         <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>82</v>
@@ -15369,7 +15372,7 @@
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -15387,7 +15390,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15402,7 +15405,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -15411,7 +15414,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -15419,10 +15422,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15448,16 +15451,16 @@
         <v>132</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -15467,10 +15470,10 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>82</v>
@@ -15506,7 +15509,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15521,7 +15524,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -15530,7 +15533,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -15538,10 +15541,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15567,13 +15570,13 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15587,7 +15590,7 @@
         <v>82</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>82</v>
@@ -15623,7 +15626,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15638,7 +15641,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -15647,7 +15650,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15655,10 +15658,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15684,10 +15687,10 @@
         <v>371</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15738,7 +15741,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15753,7 +15756,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -15762,7 +15765,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15770,10 +15773,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15796,16 +15799,16 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15855,7 +15858,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15870,7 +15873,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -15879,7 +15882,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15887,13 +15890,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>82</v>
@@ -15915,17 +15918,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15974,7 +15977,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15989,16 +15992,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -16006,10 +16009,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16121,10 +16124,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16238,10 +16241,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16267,16 +16270,16 @@
         <v>173</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -16286,7 +16289,7 @@
         <v>82</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>82</v>
@@ -16304,10 +16307,10 @@
         <v>241</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -16325,7 +16328,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -16340,7 +16343,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>82</v>
@@ -16357,10 +16360,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16383,19 +16386,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -16405,7 +16408,7 @@
         <v>82</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>82</v>
@@ -16424,7 +16427,7 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -16442,7 +16445,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -16457,7 +16460,7 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>82</v>
@@ -16466,7 +16469,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -16474,10 +16477,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16503,16 +16506,16 @@
         <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -16522,10 +16525,10 @@
         <v>82</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>82</v>
@@ -16561,7 +16564,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16576,7 +16579,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
@@ -16585,7 +16588,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16593,10 +16596,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16622,13 +16625,13 @@
         <v>104</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16642,7 +16645,7 @@
         <v>82</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>82</v>
@@ -16678,7 +16681,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16693,7 +16696,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>82</v>
@@ -16702,7 +16705,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16710,10 +16713,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16739,10 +16742,10 @@
         <v>371</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16793,7 +16796,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16808,7 +16811,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>82</v>
@@ -16817,7 +16820,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16825,10 +16828,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16851,16 +16854,16 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16910,7 +16913,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16925,7 +16928,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>82</v>
@@ -16934,7 +16937,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16942,13 +16945,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
@@ -16970,17 +16973,17 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -17029,7 +17032,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17044,16 +17047,16 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -17061,10 +17064,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17176,10 +17179,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17293,10 +17296,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17322,16 +17325,16 @@
         <v>173</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -17341,7 +17344,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -17359,10 +17362,10 @@
         <v>241</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>82</v>
@@ -17380,7 +17383,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17395,7 +17398,7 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>82</v>
@@ -17412,10 +17415,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17438,19 +17441,19 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -17460,7 +17463,7 @@
         <v>82</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>82</v>
@@ -17479,7 +17482,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -17497,7 +17500,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17512,7 +17515,7 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
@@ -17521,7 +17524,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -17529,10 +17532,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17558,16 +17561,16 @@
         <v>132</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17577,10 +17580,10 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>82</v>
@@ -17616,7 +17619,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17631,7 +17634,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -17640,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -17648,10 +17651,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17677,13 +17680,13 @@
         <v>104</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17697,7 +17700,7 @@
         <v>82</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>82</v>
@@ -17733,7 +17736,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17748,7 +17751,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>82</v>
@@ -17757,7 +17760,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -17765,10 +17768,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17794,10 +17797,10 @@
         <v>371</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17848,7 +17851,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17863,7 +17866,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>82</v>
@@ -17872,7 +17875,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -17880,10 +17883,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17906,16 +17909,16 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17965,7 +17968,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17980,7 +17983,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>82</v>
@@ -17989,7 +17992,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -17997,13 +18000,13 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>82</v>
@@ -18025,17 +18028,17 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -18084,7 +18087,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -18099,16 +18102,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -18116,10 +18119,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18231,10 +18234,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18348,10 +18351,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18377,16 +18380,16 @@
         <v>173</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -18396,7 +18399,7 @@
         <v>82</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>82</v>
@@ -18414,10 +18417,10 @@
         <v>241</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -18435,7 +18438,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18450,7 +18453,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
@@ -18467,10 +18470,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18493,19 +18496,19 @@
         <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -18515,7 +18518,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>82</v>
@@ -18534,7 +18537,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -18552,7 +18555,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18567,7 +18570,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -18576,7 +18579,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -18584,10 +18587,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18613,16 +18616,16 @@
         <v>132</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -18632,10 +18635,10 @@
         <v>82</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>82</v>
@@ -18671,7 +18674,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18686,7 +18689,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -18695,7 +18698,7 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -18703,10 +18706,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18732,13 +18735,13 @@
         <v>104</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -18752,7 +18755,7 @@
         <v>82</v>
       </c>
       <c r="T130" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U130" t="s" s="2">
         <v>82</v>
@@ -18788,7 +18791,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18803,7 +18806,7 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>82</v>
@@ -18812,7 +18815,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -18820,10 +18823,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18849,10 +18852,10 @@
         <v>371</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18903,7 +18906,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18918,7 +18921,7 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>82</v>
@@ -18927,7 +18930,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18935,10 +18938,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18961,16 +18964,16 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19020,7 +19023,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -19035,7 +19038,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -19044,7 +19047,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -19052,13 +19055,13 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>82</v>
@@ -19080,17 +19083,17 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -19139,7 +19142,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -19154,16 +19157,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -19171,10 +19174,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19286,10 +19289,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19403,10 +19406,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19432,16 +19435,16 @@
         <v>173</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -19470,7 +19473,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>82</v>
@@ -19488,7 +19491,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19503,7 +19506,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -19520,10 +19523,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19546,19 +19549,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19568,7 +19571,7 @@
         <v>82</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>82</v>
@@ -19587,7 +19590,7 @@
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>82</v>
@@ -19605,7 +19608,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19620,7 +19623,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
@@ -19629,7 +19632,7 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -19637,10 +19640,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19666,16 +19669,16 @@
         <v>132</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19688,7 +19691,7 @@
         <v>82</v>
       </c>
       <c r="T138" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U138" t="s" s="2">
         <v>82</v>
@@ -19724,7 +19727,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19739,7 +19742,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
@@ -19748,7 +19751,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19756,10 +19759,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19785,13 +19788,13 @@
         <v>104</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19805,7 +19808,7 @@
         <v>82</v>
       </c>
       <c r="T139" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U139" t="s" s="2">
         <v>82</v>
@@ -19841,7 +19844,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19856,7 +19859,7 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -19865,7 +19868,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -19873,10 +19876,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19902,10 +19905,10 @@
         <v>371</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19956,7 +19959,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19971,7 +19974,7 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -19980,7 +19983,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19988,10 +19991,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20014,16 +20017,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20073,7 +20076,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20088,7 +20091,7 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
@@ -20097,7 +20100,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -20105,13 +20108,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
@@ -20133,17 +20136,17 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -20192,7 +20195,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -20207,16 +20210,16 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -20224,10 +20227,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20339,10 +20342,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20456,10 +20459,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20485,16 +20488,16 @@
         <v>173</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -20504,7 +20507,7 @@
         <v>82</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>82</v>
@@ -20522,10 +20525,10 @@
         <v>241</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
@@ -20543,7 +20546,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20558,7 +20561,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>82</v>
@@ -20575,10 +20578,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20601,19 +20604,19 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20623,7 +20626,7 @@
         <v>82</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>82</v>
@@ -20642,7 +20645,7 @@
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -20660,7 +20663,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20675,7 +20678,7 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20684,7 +20687,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20692,10 +20695,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20721,16 +20724,16 @@
         <v>132</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -20743,7 +20746,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -20779,7 +20782,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20794,7 +20797,7 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>82</v>
@@ -20803,7 +20806,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20811,10 +20814,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20840,13 +20843,13 @@
         <v>104</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20860,7 +20863,7 @@
         <v>82</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>82</v>
@@ -20896,7 +20899,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20911,7 +20914,7 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>82</v>
@@ -20920,7 +20923,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20928,10 +20931,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20957,10 +20960,10 @@
         <v>371</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -21011,7 +21014,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21026,7 +21029,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>82</v>
@@ -21035,7 +21038,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -21043,10 +21046,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21069,16 +21072,16 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -21128,7 +21131,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21143,7 +21146,7 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>82</v>
@@ -21152,7 +21155,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -21160,13 +21163,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>82</v>
@@ -21188,17 +21191,17 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -21247,7 +21250,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -21262,16 +21265,16 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -21279,10 +21282,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21394,10 +21397,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21511,10 +21514,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21540,16 +21543,16 @@
         <v>173</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21578,7 +21581,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>82</v>
@@ -21596,7 +21599,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21611,7 +21614,7 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>82</v>
@@ -21628,10 +21631,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21654,19 +21657,19 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21676,7 +21679,7 @@
         <v>82</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>82</v>
@@ -21694,10 +21697,10 @@
         <v>155</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>82</v>
@@ -21715,7 +21718,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21730,7 +21733,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>82</v>
@@ -21739,7 +21742,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21747,10 +21750,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21776,16 +21779,16 @@
         <v>132</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21795,10 +21798,10 @@
         <v>82</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="T156" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U156" t="s" s="2">
         <v>82</v>
@@ -21834,7 +21837,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21849,7 +21852,7 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>82</v>
@@ -21858,7 +21861,7 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21866,10 +21869,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21895,13 +21898,13 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21915,7 +21918,7 @@
         <v>82</v>
       </c>
       <c r="T157" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U157" t="s" s="2">
         <v>82</v>
@@ -21951,7 +21954,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21966,7 +21969,7 @@
         <v>102</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>82</v>
@@ -21975,7 +21978,7 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
@@ -21983,10 +21986,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22012,10 +22015,10 @@
         <v>371</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -22066,7 +22069,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -22081,7 +22084,7 @@
         <v>102</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>82</v>
@@ -22090,7 +22093,7 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>82</v>
@@ -22098,10 +22101,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22124,16 +22127,16 @@
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22183,7 +22186,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22198,7 +22201,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -22207,7 +22210,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -22215,13 +22218,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>82</v>
@@ -22243,17 +22246,17 @@
         <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
@@ -22302,7 +22305,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -22317,16 +22320,16 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -22334,10 +22337,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22449,10 +22452,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22566,10 +22569,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22595,16 +22598,16 @@
         <v>173</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22614,7 +22617,7 @@
         <v>82</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>82</v>
@@ -22632,10 +22635,10 @@
         <v>241</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22653,7 +22656,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22668,7 +22671,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>82</v>
@@ -22685,10 +22688,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22711,19 +22714,19 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22733,7 +22736,7 @@
         <v>82</v>
       </c>
       <c r="S164" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="T164" t="s" s="2">
         <v>82</v>
@@ -22751,10 +22754,10 @@
         <v>155</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22772,7 +22775,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22787,7 +22790,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>82</v>
@@ -22796,7 +22799,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22804,10 +22807,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22833,16 +22836,16 @@
         <v>132</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22852,10 +22855,10 @@
         <v>82</v>
       </c>
       <c r="S165" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="T165" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U165" t="s" s="2">
         <v>82</v>
@@ -22891,7 +22894,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22906,7 +22909,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>82</v>
@@ -22915,7 +22918,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22923,10 +22926,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22952,13 +22955,13 @@
         <v>104</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22972,7 +22975,7 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U166" t="s" s="2">
         <v>82</v>
@@ -23008,7 +23011,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -23023,7 +23026,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>82</v>
@@ -23032,7 +23035,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -23040,10 +23043,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23069,10 +23072,10 @@
         <v>371</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -23123,7 +23126,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -23138,7 +23141,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>82</v>
@@ -23147,7 +23150,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -23155,10 +23158,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23181,16 +23184,16 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23240,7 +23243,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23255,7 +23258,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>82</v>
@@ -23264,7 +23267,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -23272,13 +23275,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>82</v>
@@ -23300,17 +23303,17 @@
         <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -23359,7 +23362,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23374,16 +23377,16 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -23391,10 +23394,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23506,10 +23509,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23623,10 +23626,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23652,16 +23655,16 @@
         <v>173</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23671,7 +23674,7 @@
         <v>82</v>
       </c>
       <c r="S172" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T172" t="s" s="2">
         <v>82</v>
@@ -23689,10 +23692,10 @@
         <v>241</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>82</v>
@@ -23710,7 +23713,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23725,7 +23728,7 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
@@ -23742,10 +23745,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23768,19 +23771,19 @@
         <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -23790,7 +23793,7 @@
         <v>82</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>82</v>
@@ -23808,10 +23811,10 @@
         <v>155</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -23829,7 +23832,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23844,7 +23847,7 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>82</v>
@@ -23853,7 +23856,7 @@
         <v>82</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>82</v>
@@ -23861,10 +23864,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23890,16 +23893,16 @@
         <v>132</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -23909,10 +23912,10 @@
         <v>82</v>
       </c>
       <c r="S174" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="T174" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U174" t="s" s="2">
         <v>82</v>
@@ -23948,7 +23951,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23963,7 +23966,7 @@
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>82</v>
@@ -23972,7 +23975,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23980,10 +23983,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24009,13 +24012,13 @@
         <v>104</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -24029,7 +24032,7 @@
         <v>82</v>
       </c>
       <c r="T175" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U175" t="s" s="2">
         <v>82</v>
@@ -24065,7 +24068,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -24080,7 +24083,7 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>82</v>
@@ -24089,7 +24092,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
@@ -24097,10 +24100,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24126,10 +24129,10 @@
         <v>371</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24180,7 +24183,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24195,7 +24198,7 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>82</v>
@@ -24204,7 +24207,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -24212,10 +24215,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24238,16 +24241,16 @@
         <v>91</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -24297,7 +24300,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24312,7 +24315,7 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>82</v>
@@ -24321,7 +24324,7 @@
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -24329,13 +24332,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D178" t="s" s="2">
         <v>82</v>
@@ -24357,17 +24360,17 @@
         <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -24416,7 +24419,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24431,16 +24434,16 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
@@ -24448,10 +24451,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24563,10 +24566,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24680,10 +24683,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24709,16 +24712,16 @@
         <v>173</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24747,7 +24750,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>82</v>
@@ -24765,7 +24768,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24780,7 +24783,7 @@
         <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>82</v>
@@ -24797,10 +24800,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24823,19 +24826,19 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -24845,7 +24848,7 @@
         <v>82</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>82</v>
@@ -24863,10 +24866,10 @@
         <v>155</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>82</v>
@@ -24884,7 +24887,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24899,7 +24902,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>82</v>
@@ -24908,7 +24911,7 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
@@ -24916,10 +24919,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24945,16 +24948,16 @@
         <v>132</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24964,10 +24967,10 @@
         <v>82</v>
       </c>
       <c r="S183" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="T183" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="U183" t="s" s="2">
         <v>82</v>
@@ -25003,7 +25006,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -25018,7 +25021,7 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>82</v>
@@ -25027,7 +25030,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -25035,10 +25038,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25064,13 +25067,13 @@
         <v>104</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -25084,7 +25087,7 @@
         <v>82</v>
       </c>
       <c r="T184" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="U184" t="s" s="2">
         <v>82</v>
@@ -25120,7 +25123,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -25135,7 +25138,7 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>82</v>
@@ -25144,7 +25147,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
@@ -25152,10 +25155,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25181,10 +25184,10 @@
         <v>371</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -25235,7 +25238,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -25250,7 +25253,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>82</v>
@@ -25259,7 +25262,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>82</v>
@@ -25267,10 +25270,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25293,16 +25296,16 @@
         <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -25352,7 +25355,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25367,7 +25370,7 @@
         <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL186" t="s" s="2">
         <v>82</v>
@@ -25376,7 +25379,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>82</v>
@@ -25384,10 +25387,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25410,70 +25413,70 @@
         <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q187" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="R187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF187" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q187" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="R187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25488,13 +25491,13 @@
         <v>102</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -25505,10 +25508,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25531,19 +25534,19 @@
         <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
@@ -25580,7 +25583,7 @@
         <v>82</v>
       </c>
       <c r="AB188" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AC188" s="2"/>
       <c r="AD188" t="s" s="2">
@@ -25590,7 +25593,7 @@
         <v>117</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25602,19 +25605,19 @@
         <v>82</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>
@@ -25622,13 +25625,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>82</v>
@@ -25650,19 +25653,19 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
@@ -25711,7 +25714,7 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -25723,19 +25726,19 @@
         <v>82</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>82</v>
@@ -25743,10 +25746,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25858,10 +25861,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25975,10 +25978,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26004,16 +26007,16 @@
         <v>173</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -26023,7 +26026,7 @@
         <v>82</v>
       </c>
       <c r="S192" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="T192" t="s" s="2">
         <v>82</v>
@@ -26041,10 +26044,10 @@
         <v>241</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -26062,7 +26065,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -26086,7 +26089,7 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>82</v>
@@ -26094,10 +26097,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26123,13 +26126,13 @@
         <v>104</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O193" t="s" s="2">
         <v>262</v>
@@ -26181,7 +26184,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -26205,7 +26208,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -26213,14 +26216,14 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -26242,13 +26245,13 @@
         <v>104</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26262,7 +26265,7 @@
         <v>82</v>
       </c>
       <c r="T194" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="U194" t="s" s="2">
         <v>82</v>
@@ -26298,7 +26301,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26313,7 +26316,7 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>82</v>
@@ -26322,7 +26325,7 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>82</v>
@@ -26330,14 +26333,14 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -26359,13 +26362,13 @@
         <v>104</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -26415,7 +26418,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26430,7 +26433,7 @@
         <v>102</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>82</v>
@@ -26439,7 +26442,7 @@
         <v>82</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>82</v>
@@ -26447,10 +26450,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26476,10 +26479,10 @@
         <v>104</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26530,7 +26533,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26545,7 +26548,7 @@
         <v>102</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>82</v>
@@ -26554,7 +26557,7 @@
         <v>82</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
@@ -26562,10 +26565,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26591,10 +26594,10 @@
         <v>104</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26645,7 +26648,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26660,7 +26663,7 @@
         <v>102</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>82</v>
@@ -26669,7 +26672,7 @@
         <v>82</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>
@@ -26677,10 +26680,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26706,14 +26709,14 @@
         <v>371</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>82</v>
@@ -26762,7 +26765,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -26786,7 +26789,7 @@
         <v>82</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>82</v>
@@ -26794,13 +26797,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D199" t="s" s="2">
         <v>82</v>
@@ -26822,19 +26825,19 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>82</v>
@@ -26883,7 +26886,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -26895,19 +26898,19 @@
         <v>82</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -26915,10 +26918,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27030,10 +27033,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27145,13 +27148,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>82</v>
@@ -27173,13 +27176,13 @@
         <v>82</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -27262,10 +27265,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27291,16 +27294,16 @@
         <v>173</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>82</v>
@@ -27310,7 +27313,7 @@
         <v>82</v>
       </c>
       <c r="S203" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>82</v>
@@ -27328,10 +27331,10 @@
         <v>241</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>82</v>
@@ -27349,7 +27352,7 @@
         <v>82</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -27373,7 +27376,7 @@
         <v>82</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>82</v>
@@ -27381,10 +27384,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27410,13 +27413,13 @@
         <v>104</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O204" t="s" s="2">
         <v>262</v>
@@ -27468,7 +27471,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -27492,7 +27495,7 @@
         <v>82</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>82</v>
@@ -27500,14 +27503,14 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
@@ -27529,13 +27532,13 @@
         <v>104</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27549,7 +27552,7 @@
         <v>82</v>
       </c>
       <c r="T205" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="U205" t="s" s="2">
         <v>82</v>
@@ -27585,7 +27588,7 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -27600,7 +27603,7 @@
         <v>102</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AL205" t="s" s="2">
         <v>82</v>
@@ -27609,7 +27612,7 @@
         <v>82</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>82</v>
@@ -27617,14 +27620,14 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
@@ -27646,13 +27649,13 @@
         <v>104</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -27702,7 +27705,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -27717,7 +27720,7 @@
         <v>102</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AL206" t="s" s="2">
         <v>82</v>
@@ -27726,7 +27729,7 @@
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>82</v>
@@ -27734,10 +27737,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27763,10 +27766,10 @@
         <v>104</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -27817,7 +27820,7 @@
         <v>82</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27832,7 +27835,7 @@
         <v>102</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>82</v>
@@ -27841,7 +27844,7 @@
         <v>82</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>82</v>
@@ -27849,10 +27852,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27878,10 +27881,10 @@
         <v>104</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -27932,7 +27935,7 @@
         <v>82</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -27947,7 +27950,7 @@
         <v>102</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AL208" t="s" s="2">
         <v>82</v>
@@ -27956,7 +27959,7 @@
         <v>82</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>82</v>
@@ -27964,10 +27967,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27993,14 +27996,14 @@
         <v>371</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>82</v>
@@ -28049,7 +28052,7 @@
         <v>82</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -28073,7 +28076,7 @@
         <v>82</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>82</v>
@@ -28081,10 +28084,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28107,19 +28110,19 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>82</v>
@@ -28168,7 +28171,7 @@
         <v>82</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -28183,16 +28186,16 @@
         <v>102</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AM210" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>82</v>
@@ -28200,10 +28203,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28229,16 +28232,16 @@
         <v>173</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>82</v>
@@ -28267,7 +28270,7 @@
       </c>
       <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>82</v>
@@ -28285,7 +28288,7 @@
         <v>82</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -28300,16 +28303,16 @@
         <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AM211" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>82</v>
@@ -28317,10 +28320,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28343,19 +28346,19 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>82</v>
@@ -28404,7 +28407,7 @@
         <v>82</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -28419,27 +28422,27 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28462,19 +28465,19 @@
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>82</v>
@@ -28523,7 +28526,7 @@
         <v>82</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28538,7 +28541,7 @@
         <v>102</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>108</v>
@@ -28547,7 +28550,7 @@
         <v>82</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>82</v>
@@ -28555,10 +28558,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28584,16 +28587,16 @@
         <v>220</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>82</v>
@@ -28642,7 +28645,7 @@
         <v>82</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -28657,16 +28660,16 @@
         <v>102</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>82</v>
@@ -28674,10 +28677,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28700,17 +28703,17 @@
         <v>82</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>82</v>
@@ -28739,7 +28742,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>82</v>
@@ -28757,7 +28760,7 @@
         <v>82</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28772,16 +28775,16 @@
         <v>102</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AM215" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>82</v>
@@ -28789,10 +28792,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28815,19 +28818,19 @@
         <v>82</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>82</v>
@@ -28876,7 +28879,7 @@
         <v>82</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -28891,7 +28894,7 @@
         <v>102</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>108</v>
@@ -28900,7 +28903,7 @@
         <v>82</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>82</v>
@@ -28908,10 +28911,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28934,19 +28937,19 @@
         <v>82</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>82</v>
@@ -28995,7 +28998,7 @@
         <v>82</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -29010,7 +29013,7 @@
         <v>102</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AL217" t="s" s="2">
         <v>108</v>
@@ -29019,7 +29022,7 @@
         <v>82</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>82</v>
@@ -29027,10 +29030,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29053,19 +29056,19 @@
         <v>82</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>82</v>
@@ -29114,7 +29117,7 @@
         <v>82</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -29126,10 +29129,10 @@
         <v>82</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AL218" t="s" s="2">
         <v>108</v>
@@ -29146,10 +29149,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29261,10 +29264,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29374,13 +29377,13 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="B221" t="s" s="2">
         <v>875</v>
       </c>
-      <c r="B221" t="s" s="2">
-        <v>874</v>
-      </c>
       <c r="C221" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D221" t="s" s="2">
         <v>82</v>
@@ -29402,13 +29405,13 @@
         <v>82</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -29491,13 +29494,13 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>82</v>
@@ -29519,13 +29522,13 @@
         <v>82</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -29608,14 +29611,14 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
@@ -29637,16 +29640,16 @@
         <v>111</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N223" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>82</v>
@@ -29695,7 +29698,7 @@
         <v>82</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -29727,10 +29730,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29753,17 +29756,17 @@
         <v>82</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>82</v>
@@ -29791,16 +29794,16 @@
         <v>155</v>
       </c>
       <c r="Y224" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="Z224" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AC224" s="2"/>
       <c r="AD224" t="s" s="2">
@@ -29810,7 +29813,7 @@
         <v>117</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -29825,7 +29828,7 @@
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>108</v>
@@ -29834,7 +29837,7 @@
         <v>82</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>82</v>
@@ -29842,13 +29845,13 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D225" t="s" s="2">
         <v>82</v>
@@ -29870,17 +29873,17 @@
         <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>82</v>
@@ -29909,7 +29912,7 @@
       </c>
       <c r="Y225" s="2"/>
       <c r="Z225" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>82</v>
@@ -29927,7 +29930,7 @@
         <v>82</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -29942,7 +29945,7 @@
         <v>102</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AL225" t="s" s="2">
         <v>108</v>
@@ -29951,7 +29954,7 @@
         <v>82</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>82</v>
@@ -29959,10 +29962,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30074,10 +30077,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30189,13 +30192,13 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B228" t="s" s="2">
         <v>906</v>
       </c>
-      <c r="B228" t="s" s="2">
-        <v>905</v>
-      </c>
       <c r="C228" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>82</v>
@@ -30217,13 +30220,13 @@
         <v>82</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -30306,10 +30309,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30421,10 +30424,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30536,10 +30539,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30579,7 +30582,7 @@
       </c>
       <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="S231" t="s" s="2">
         <v>82</v>
@@ -30653,10 +30656,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30685,7 +30688,7 @@
         <v>221</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -30697,7 +30700,7 @@
         <v>82</v>
       </c>
       <c r="S232" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="T232" t="s" s="2">
         <v>82</v>
@@ -30716,7 +30719,7 @@
       </c>
       <c r="Y232" s="2"/>
       <c r="Z232" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>82</v>
@@ -30766,10 +30769,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30795,16 +30798,16 @@
         <v>151</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>82</v>
@@ -30853,7 +30856,7 @@
         <v>82</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -30868,7 +30871,7 @@
         <v>102</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>82</v>
@@ -30877,7 +30880,7 @@
         <v>82</v>
       </c>
       <c r="AN233" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="AO233" t="s" s="2">
         <v>82</v>
@@ -30885,10 +30888,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30914,16 +30917,16 @@
         <v>104</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>82</v>
@@ -30972,7 +30975,7 @@
         <v>82</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
@@ -30987,7 +30990,7 @@
         <v>102</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>82</v>
@@ -30996,7 +30999,7 @@
         <v>82</v>
       </c>
       <c r="AN234" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AO234" t="s" s="2">
         <v>82</v>
@@ -31004,13 +31007,13 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D235" t="s" s="2">
         <v>82</v>
@@ -31032,17 +31035,17 @@
         <v>82</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>82</v>
@@ -31071,7 +31074,7 @@
       </c>
       <c r="Y235" s="2"/>
       <c r="Z235" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="AA235" t="s" s="2">
         <v>82</v>
@@ -31089,7 +31092,7 @@
         <v>82</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -31104,7 +31107,7 @@
         <v>102</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AL235" t="s" s="2">
         <v>108</v>
@@ -31113,7 +31116,7 @@
         <v>82</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>82</v>
@@ -31121,10 +31124,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31236,10 +31239,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31351,13 +31354,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>82</v>
@@ -31379,13 +31382,13 @@
         <v>82</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -31468,10 +31471,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31583,10 +31586,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31698,10 +31701,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31741,7 +31744,7 @@
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="S241" t="s" s="2">
         <v>82</v>
@@ -31815,10 +31818,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31847,7 +31850,7 @@
         <v>221</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -31859,7 +31862,7 @@
         <v>82</v>
       </c>
       <c r="S242" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="T242" t="s" s="2">
         <v>82</v>
@@ -31878,7 +31881,7 @@
       </c>
       <c r="Y242" s="2"/>
       <c r="Z242" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>82</v>
@@ -31928,10 +31931,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31957,16 +31960,16 @@
         <v>151</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>82</v>
@@ -32015,7 +32018,7 @@
         <v>82</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -32030,7 +32033,7 @@
         <v>102</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AL243" t="s" s="2">
         <v>82</v>
@@ -32039,7 +32042,7 @@
         <v>82</v>
       </c>
       <c r="AN243" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="AO243" t="s" s="2">
         <v>82</v>
@@ -32047,10 +32050,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -32076,16 +32079,16 @@
         <v>104</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>82</v>
@@ -32134,7 +32137,7 @@
         <v>82</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
@@ -32149,7 +32152,7 @@
         <v>102</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>82</v>
@@ -32158,7 +32161,7 @@
         <v>82</v>
       </c>
       <c r="AN244" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AO244" t="s" s="2">
         <v>82</v>
@@ -32166,10 +32169,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -32192,17 +32195,17 @@
         <v>82</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>82</v>
@@ -32251,7 +32254,7 @@
         <v>82</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>80</v>
@@ -32266,7 +32269,7 @@
         <v>102</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>108</v>
@@ -32275,7 +32278,7 @@
         <v>82</v>
       </c>
       <c r="AN245" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="AO245" t="s" s="2">
         <v>82</v>
@@ -32283,10 +32286,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -32309,19 +32312,19 @@
         <v>82</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>82</v>
@@ -32370,7 +32373,7 @@
         <v>82</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>80</v>
@@ -32385,7 +32388,7 @@
         <v>102</v>
       </c>
       <c r="AK246" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AL246" t="s" s="2">
         <v>108</v>
@@ -32394,7 +32397,7 @@
         <v>82</v>
       </c>
       <c r="AN246" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AO246" t="s" s="2">
         <v>82</v>
@@ -32402,10 +32405,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32428,17 +32431,17 @@
         <v>82</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>82</v>
@@ -32487,7 +32490,7 @@
         <v>82</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>80</v>
@@ -32502,7 +32505,7 @@
         <v>102</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AL247" t="s" s="2">
         <v>108</v>
@@ -32511,7 +32514,7 @@
         <v>82</v>
       </c>
       <c r="AN247" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AO247" t="s" s="2">
         <v>82</v>
@@ -32519,10 +32522,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32548,14 +32551,14 @@
         <v>173</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>82</v>
@@ -32583,10 +32586,10 @@
         <v>241</v>
       </c>
       <c r="Y248" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="Z248" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AA248" t="s" s="2">
         <v>82</v>
@@ -32604,7 +32607,7 @@
         <v>82</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>80</v>
@@ -32619,7 +32622,7 @@
         <v>102</v>
       </c>
       <c r="AK248" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AL248" t="s" s="2">
         <v>108</v>
@@ -32628,7 +32631,7 @@
         <v>82</v>
       </c>
       <c r="AN248" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AO248" t="s" s="2">
         <v>82</v>
@@ -32636,10 +32639,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32662,17 +32665,17 @@
         <v>82</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="P249" t="s" s="2">
         <v>82</v>
@@ -32721,7 +32724,7 @@
         <v>82</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>80</v>
@@ -32730,13 +32733,13 @@
         <v>90</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK249" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AL249" t="s" s="2">
         <v>108</v>
@@ -32745,7 +32748,7 @@
         <v>82</v>
       </c>
       <c r="AN249" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AO249" t="s" s="2">
         <v>82</v>
@@ -32753,10 +32756,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32782,10 +32785,10 @@
         <v>371</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
@@ -32836,7 +32839,7 @@
         <v>82</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>80</v>
@@ -32851,7 +32854,7 @@
         <v>102</v>
       </c>
       <c r="AK250" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AL250" t="s" s="2">
         <v>108</v>
@@ -32868,10 +32871,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32894,19 +32897,19 @@
         <v>82</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>82</v>
@@ -32955,7 +32958,7 @@
         <v>82</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>80</v>
@@ -32970,10 +32973,10 @@
         <v>102</v>
       </c>
       <c r="AK251" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="AL251" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="AM251" t="s" s="2">
         <v>82</v>
@@ -32987,10 +32990,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -33102,10 +33105,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -33219,14 +33222,14 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E254" s="2"/>
       <c r="F254" t="s" s="2">
@@ -33248,16 +33251,16 @@
         <v>111</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N254" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O254" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P254" t="s" s="2">
         <v>82</v>
@@ -33306,7 +33309,7 @@
         <v>82</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
@@ -33338,10 +33341,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -33364,19 +33367,19 @@
         <v>82</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="N255" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="O255" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>82</v>
@@ -33425,7 +33428,7 @@
         <v>82</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>90</v>
@@ -33440,16 +33443,16 @@
         <v>102</v>
       </c>
       <c r="AK255" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="AM255" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN255" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="AO255" t="s" s="2">
         <v>82</v>
@@ -33457,10 +33460,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -33483,19 +33486,19 @@
         <v>82</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="O256" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="P256" t="s" s="2">
         <v>82</v>
@@ -33544,7 +33547,7 @@
         <v>82</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>80</v>
@@ -33559,16 +33562,16 @@
         <v>102</v>
       </c>
       <c r="AK256" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="AM256" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN256" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="AO256" t="s" s="2">
         <v>82</v>
@@ -33576,14 +33579,14 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
@@ -33602,16 +33605,16 @@
         <v>82</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
@@ -33661,7 +33664,7 @@
         <v>82</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>80</v>
@@ -33676,7 +33679,7 @@
         <v>102</v>
       </c>
       <c r="AK257" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AL257" t="s" s="2">
         <v>108</v>
@@ -33685,7 +33688,7 @@
         <v>82</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>82</v>
@@ -33693,10 +33696,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33719,19 +33722,19 @@
         <v>91</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O258" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>82</v>
@@ -33780,7 +33783,7 @@
         <v>82</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>80</v>
@@ -33795,10 +33798,10 @@
         <v>102</v>
       </c>
       <c r="AK258" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AM258" t="s" s="2">
         <v>82</v>
@@ -33812,10 +33815,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33838,19 +33841,19 @@
         <v>91</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O259" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="P259" t="s" s="2">
         <v>82</v>
@@ -33899,7 +33902,7 @@
         <v>82</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>80</v>
@@ -33914,7 +33917,7 @@
         <v>102</v>
       </c>
       <c r="AK259" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AL259" t="s" s="2">
         <v>108</v>
@@ -33931,10 +33934,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -34046,10 +34049,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -34163,14 +34166,14 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
@@ -34192,16 +34195,16 @@
         <v>111</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="N262" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O262" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P262" t="s" s="2">
         <v>82</v>
@@ -34250,7 +34253,7 @@
         <v>82</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>80</v>
@@ -34282,10 +34285,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -34308,16 +34311,16 @@
         <v>91</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
@@ -34367,7 +34370,7 @@
         <v>82</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>90</v>
@@ -34382,7 +34385,7 @@
         <v>102</v>
       </c>
       <c r="AK263" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL263" t="s" s="2">
         <v>108</v>
@@ -34391,7 +34394,7 @@
         <v>82</v>
       </c>
       <c r="AN263" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AO263" t="s" s="2">
         <v>82</v>
@@ -34399,10 +34402,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -34428,10 +34431,10 @@
         <v>173</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34461,10 +34464,10 @@
         <v>241</v>
       </c>
       <c r="Y264" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="Z264" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>82</v>
@@ -34482,7 +34485,7 @@
         <v>82</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>90</v>
@@ -34497,7 +34500,7 @@
         <v>102</v>
       </c>
       <c r="AK264" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AL264" t="s" s="2">
         <v>108</v>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1328,10 +1328,10 @@
     <t>methodCollection</t>
   </si>
   <si>
-    <t>Channel used to collect the identity traits or the INS | Canal d'obtention des traits d'identité ou de l'INS (SM, CV, INSi, CB, RFID, AV)</t>
-  </si>
-  <si>
-    <t>Précise le canal technique par lequel les traits d'identité ou l'INS ont été obtenus (RNIV §4.3) : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>
+    <t>Canal d'obtention des traits d'identité ou de l'INS (SM, CV, INSi, CB, RFID, AV) | Channel used to collect the identity traits or the INS</t>
+  </si>
+  <si>
+    <t>Précise le canal technique par lequel les traits d'identité ou l'INS ont été obtenus : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:methodCollection.id</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1331,7 +1331,7 @@
     <t>Canal d'obtention des traits d'identité ou de l'INS (SM, CV, INSi, CB, RFID, AV) | Channel used to collect the identity traits or the INS</t>
   </si>
   <si>
-    <t>Précise le canal technique par lequel les traits d'identité ou l'INS ont été obtenus : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>
+    <t>Précise le canal par lequel les traits d'identité ou l'INS ont été obtenus : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:methodCollection.id</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1308,12 +1308,11 @@
 </t>
   </si>
   <si>
-    <t>Reliabilility of the identity | Fiabilité de l'identité</t>
-  </si>
-  <si>
-    <t>Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) accompagné de la méthode de collection.
--Reliabilility of the patient's identity</t>
+    <t>FR Core Patient Identity Reliability Extension</t>
+  </si>
+  <si>
+    <t>Extension composite précisant le degré de confiance de l'identité du patient au sens du Référentiel National d'Identitovigilance (RNIV) : statut de confiance (provisoire, récupérée, validée, qualifiée), canal d'obtention des traits d'identité ou de l'INS, pièce justificative contrôlée, dates associées et annotations complémentaires.
+Composite extension specifying the confidence level of a patient's identity per the French National Identity Vigilance Framework (RNIV): trust status (provisional, recovered, validated, qualified), channel used to collect the identity traits or the INS, validation evidence, related dates and additional annotations.</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.id</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9781" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9781" uniqueCount="1050">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1369,7 +1369,10 @@
     <t>dateCollection</t>
   </si>
   <si>
-    <t>INS collection date| date d'interrogation du téléservice INSi</t>
+    <t>Date d'obtention des traits d'identité ou de l'INS | Date the identity traits or the INS were collected</t>
+  </si>
+  <si>
+    <t>Date à laquelle les traits d'identité ou l'INS ont été obtenus, quel que soit le canal utilisé (cf. sous-extension `methodCollection`) : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID. Cette date ne doit pas être confondue avec la date de vérification de l'identité (cf. sous-extension `validationDate`). | Date at which the identity traits or the INS were obtained, regardless of the channel used (see the `methodCollection` sub-extension): manual entry, Vitale card reading, direct query of the INSi teleservice, barcode/Datamatrix scan, RFID reading. This date must not be confused with the identity verification date (see the `validationDate` sub-extension).</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:dateCollection.id</t>
@@ -1430,6 +1433,10 @@
     <t>Patient.extension:identityReliability.extension:comment.value[x]</t>
   </si>
   <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-status-comment|2.2.0</t>
   </si>
   <si>
@@ -1439,7 +1446,10 @@
     <t>validationDate</t>
   </si>
   <si>
-    <t>Date de vérification de l'identité</t>
+    <t>Date de vérification de l'identité | Identity verification date</t>
+  </si>
+  <si>
+    <t>Date à laquelle l'identité a été vérifiée sur la base de la pièce justificative contrôlée (cf. sous-extension `validationMode`). | Date at which the identity was verified based on the checked supporting document (see the `validationMode` sub-extension).</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:validationDate.id</t>
@@ -1631,10 +1641,6 @@
   </si>
   <si>
     <t>Patient.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Description of identifier</t>
@@ -11277,7 +11283,7 @@
         <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11360,7 +11366,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>423</v>
@@ -11475,7 +11481,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>425</v>
@@ -11590,7 +11596,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>427</v>
@@ -11707,7 +11713,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>429</v>
@@ -11733,7 +11739,7 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>221</v>
@@ -11822,13 +11828,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>82</v>
@@ -11939,7 +11945,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>423</v>
@@ -12054,7 +12060,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>425</v>
@@ -12169,7 +12175,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>427</v>
@@ -12212,7 +12218,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>82</v>
@@ -12286,7 +12292,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>429</v>
@@ -12349,7 +12355,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -12399,13 +12405,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>82</v>
@@ -12430,7 +12436,7 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>199</v>
@@ -12516,7 +12522,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>423</v>
@@ -12631,7 +12637,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>425</v>
@@ -12746,7 +12752,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>427</v>
@@ -12789,7 +12795,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>82</v>
@@ -12863,7 +12869,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>429</v>
@@ -12889,7 +12895,7 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>151</v>
+        <v>455</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>221</v>
@@ -12926,7 +12932,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12976,13 +12982,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>82</v>
@@ -13007,10 +13013,10 @@
         <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>199</v>
+        <v>460</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -13093,7 +13099,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>423</v>
@@ -13208,7 +13214,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>425</v>
@@ -13323,7 +13329,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>427</v>
@@ -13366,7 +13372,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>82</v>
@@ -13440,7 +13446,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>429</v>
@@ -13466,7 +13472,7 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>221</v>
@@ -13555,13 +13561,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
@@ -13672,7 +13678,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>423</v>
@@ -13787,7 +13793,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>425</v>
@@ -13902,7 +13908,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>427</v>
@@ -13945,7 +13951,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>82</v>
@@ -14019,7 +14025,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>429</v>
@@ -14082,7 +14088,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -14132,7 +14138,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>212</v>
@@ -14175,7 +14181,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -14249,7 +14255,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>219</v>
@@ -14275,7 +14281,7 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>221</v>
@@ -14364,13 +14370,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>82</v>
@@ -14392,13 +14398,13 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14481,13 +14487,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>82</v>
@@ -14509,13 +14515,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14598,10 +14604,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14627,16 +14633,16 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14685,7 +14691,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14717,10 +14723,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14743,17 +14749,17 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14790,10 +14796,10 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
@@ -14802,7 +14808,7 @@
         <v>117</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14817,16 +14823,16 @@
         <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14834,13 +14840,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>82</v>
@@ -14862,17 +14868,17 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14921,7 +14927,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14936,16 +14942,16 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14953,10 +14959,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15068,10 +15074,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15185,10 +15191,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15214,16 +15220,16 @@
         <v>173</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15233,7 +15239,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -15251,10 +15257,10 @@
         <v>241</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -15272,7 +15278,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -15287,7 +15293,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -15304,10 +15310,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15330,19 +15336,19 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -15352,7 +15358,7 @@
         <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>82</v>
@@ -15371,7 +15377,7 @@
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -15389,7 +15395,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15404,7 +15410,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -15413,7 +15419,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -15421,10 +15427,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15450,16 +15456,16 @@
         <v>132</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -15469,10 +15475,10 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>82</v>
@@ -15508,7 +15514,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15523,7 +15529,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -15532,7 +15538,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -15540,10 +15546,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15569,13 +15575,13 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15589,7 +15595,7 @@
         <v>82</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>82</v>
@@ -15625,7 +15631,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15640,7 +15646,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -15649,7 +15655,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -15657,10 +15663,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15686,10 +15692,10 @@
         <v>371</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15740,7 +15746,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15755,7 +15761,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -15764,7 +15770,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15772,10 +15778,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15798,16 +15804,16 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15857,7 +15863,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15872,7 +15878,7 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>82</v>
@@ -15881,7 +15887,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15889,13 +15895,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>82</v>
@@ -15917,17 +15923,17 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15976,7 +15982,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15991,16 +15997,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -16008,10 +16014,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16123,10 +16129,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16240,10 +16246,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16269,16 +16275,16 @@
         <v>173</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -16288,7 +16294,7 @@
         <v>82</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>82</v>
@@ -16306,10 +16312,10 @@
         <v>241</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -16327,7 +16333,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -16342,7 +16348,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>82</v>
@@ -16359,10 +16365,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16385,19 +16391,19 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -16407,7 +16413,7 @@
         <v>82</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>82</v>
@@ -16426,7 +16432,7 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -16444,7 +16450,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -16459,7 +16465,7 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>82</v>
@@ -16468,7 +16474,7 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -16476,10 +16482,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16505,16 +16511,16 @@
         <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -16524,10 +16530,10 @@
         <v>82</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>82</v>
@@ -16563,7 +16569,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16578,7 +16584,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
@@ -16587,7 +16593,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16595,10 +16601,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16624,13 +16630,13 @@
         <v>104</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16644,7 +16650,7 @@
         <v>82</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>82</v>
@@ -16680,7 +16686,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16695,7 +16701,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>82</v>
@@ -16704,7 +16710,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16712,10 +16718,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16741,10 +16747,10 @@
         <v>371</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16795,7 +16801,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16810,7 +16816,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>82</v>
@@ -16819,7 +16825,7 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16827,10 +16833,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16853,16 +16859,16 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16912,7 +16918,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16927,7 +16933,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>82</v>
@@ -16936,7 +16942,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16944,13 +16950,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
@@ -16972,17 +16978,17 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -17031,7 +17037,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -17046,16 +17052,16 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -17063,10 +17069,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17178,10 +17184,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17295,10 +17301,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17324,16 +17330,16 @@
         <v>173</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -17343,7 +17349,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -17361,10 +17367,10 @@
         <v>241</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>82</v>
@@ -17382,7 +17388,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17397,7 +17403,7 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>82</v>
@@ -17414,10 +17420,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17440,19 +17446,19 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -17462,7 +17468,7 @@
         <v>82</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>82</v>
@@ -17481,7 +17487,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -17499,7 +17505,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17514,7 +17520,7 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>82</v>
@@ -17523,7 +17529,7 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -17531,10 +17537,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17560,16 +17566,16 @@
         <v>132</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17579,10 +17585,10 @@
         <v>82</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>82</v>
@@ -17618,7 +17624,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17633,7 +17639,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
@@ -17642,7 +17648,7 @@
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -17650,10 +17656,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17679,13 +17685,13 @@
         <v>104</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17699,7 +17705,7 @@
         <v>82</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>82</v>
@@ -17735,7 +17741,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17750,7 +17756,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>82</v>
@@ -17759,7 +17765,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -17767,10 +17773,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17796,10 +17802,10 @@
         <v>371</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17850,7 +17856,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17865,7 +17871,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>82</v>
@@ -17874,7 +17880,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -17882,10 +17888,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17908,16 +17914,16 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17967,7 +17973,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17982,7 +17988,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>82</v>
@@ -17991,7 +17997,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -17999,13 +18005,13 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>82</v>
@@ -18027,17 +18033,17 @@
         <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -18086,7 +18092,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -18101,16 +18107,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -18118,10 +18124,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18233,10 +18239,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18350,10 +18356,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18379,16 +18385,16 @@
         <v>173</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -18398,7 +18404,7 @@
         <v>82</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>82</v>
@@ -18416,10 +18422,10 @@
         <v>241</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -18437,7 +18443,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18452,7 +18458,7 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>82</v>
@@ -18469,10 +18475,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18495,19 +18501,19 @@
         <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -18517,7 +18523,7 @@
         <v>82</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>82</v>
@@ -18536,7 +18542,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -18554,7 +18560,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18569,7 +18575,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -18578,7 +18584,7 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -18586,10 +18592,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18615,16 +18621,16 @@
         <v>132</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -18634,10 +18640,10 @@
         <v>82</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>82</v>
@@ -18673,7 +18679,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18688,7 +18694,7 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -18697,7 +18703,7 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
@@ -18705,10 +18711,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18734,13 +18740,13 @@
         <v>104</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -18754,7 +18760,7 @@
         <v>82</v>
       </c>
       <c r="T130" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U130" t="s" s="2">
         <v>82</v>
@@ -18790,7 +18796,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18805,7 +18811,7 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>82</v>
@@ -18814,7 +18820,7 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -18822,10 +18828,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18851,10 +18857,10 @@
         <v>371</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18905,7 +18911,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18920,7 +18926,7 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>82</v>
@@ -18929,7 +18935,7 @@
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -18937,10 +18943,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18963,16 +18969,16 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -19022,7 +19028,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -19037,7 +19043,7 @@
         <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>82</v>
@@ -19046,7 +19052,7 @@
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -19054,13 +19060,13 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>82</v>
@@ -19082,17 +19088,17 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -19141,7 +19147,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -19156,16 +19162,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -19173,10 +19179,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19288,10 +19294,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19405,10 +19411,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19434,16 +19440,16 @@
         <v>173</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -19472,7 +19478,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>82</v>
@@ -19490,7 +19496,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19505,7 +19511,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>82</v>
@@ -19522,10 +19528,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19548,19 +19554,19 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19570,7 +19576,7 @@
         <v>82</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>82</v>
@@ -19589,7 +19595,7 @@
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>82</v>
@@ -19607,7 +19613,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19622,7 +19628,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
@@ -19631,7 +19637,7 @@
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -19639,10 +19645,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19668,16 +19674,16 @@
         <v>132</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19690,7 +19696,7 @@
         <v>82</v>
       </c>
       <c r="T138" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U138" t="s" s="2">
         <v>82</v>
@@ -19726,7 +19732,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19741,7 +19747,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
@@ -19750,7 +19756,7 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19758,10 +19764,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19787,13 +19793,13 @@
         <v>104</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19807,7 +19813,7 @@
         <v>82</v>
       </c>
       <c r="T139" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U139" t="s" s="2">
         <v>82</v>
@@ -19843,7 +19849,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19858,7 +19864,7 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -19867,7 +19873,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -19875,10 +19881,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19904,10 +19910,10 @@
         <v>371</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19958,7 +19964,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19973,7 +19979,7 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>82</v>
@@ -19982,7 +19988,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19990,10 +19996,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20016,16 +20022,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20075,7 +20081,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -20090,7 +20096,7 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
@@ -20099,7 +20105,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -20107,13 +20113,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
@@ -20135,17 +20141,17 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -20194,7 +20200,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -20209,16 +20215,16 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -20226,10 +20232,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20341,10 +20347,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20458,10 +20464,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20487,16 +20493,16 @@
         <v>173</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -20506,7 +20512,7 @@
         <v>82</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>82</v>
@@ -20524,10 +20530,10 @@
         <v>241</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
@@ -20545,7 +20551,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20560,7 +20566,7 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>82</v>
@@ -20577,10 +20583,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20603,19 +20609,19 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20625,7 +20631,7 @@
         <v>82</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>82</v>
@@ -20644,7 +20650,7 @@
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -20662,7 +20668,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20677,7 +20683,7 @@
         <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
@@ -20686,7 +20692,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20694,10 +20700,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20723,16 +20729,16 @@
         <v>132</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -20745,7 +20751,7 @@
         <v>82</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>82</v>
@@ -20781,7 +20787,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20796,7 +20802,7 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>82</v>
@@ -20805,7 +20811,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20813,10 +20819,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20842,13 +20848,13 @@
         <v>104</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20862,7 +20868,7 @@
         <v>82</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>82</v>
@@ -20898,7 +20904,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20913,7 +20919,7 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>82</v>
@@ -20922,7 +20928,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20930,10 +20936,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20959,10 +20965,10 @@
         <v>371</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -21013,7 +21019,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -21028,7 +21034,7 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>82</v>
@@ -21037,7 +21043,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -21045,10 +21051,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21071,16 +21077,16 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -21130,7 +21136,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -21145,7 +21151,7 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>82</v>
@@ -21154,7 +21160,7 @@
         <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>82</v>
@@ -21162,13 +21168,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>82</v>
@@ -21190,17 +21196,17 @@
         <v>91</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -21249,7 +21255,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -21264,16 +21270,16 @@
         <v>102</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -21281,10 +21287,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21396,10 +21402,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21513,10 +21519,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21542,16 +21548,16 @@
         <v>173</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21580,7 +21586,7 @@
       </c>
       <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>82</v>
@@ -21598,7 +21604,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21613,7 +21619,7 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>82</v>
@@ -21630,10 +21636,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21656,19 +21662,19 @@
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21678,7 +21684,7 @@
         <v>82</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>82</v>
@@ -21696,10 +21702,10 @@
         <v>155</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>82</v>
@@ -21717,7 +21723,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21732,7 +21738,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>82</v>
@@ -21741,7 +21747,7 @@
         <v>82</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21749,10 +21755,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21778,16 +21784,16 @@
         <v>132</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21797,10 +21803,10 @@
         <v>82</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="T156" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U156" t="s" s="2">
         <v>82</v>
@@ -21836,7 +21842,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21851,7 +21857,7 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>82</v>
@@ -21860,7 +21866,7 @@
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21868,10 +21874,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21897,13 +21903,13 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21917,7 +21923,7 @@
         <v>82</v>
       </c>
       <c r="T157" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U157" t="s" s="2">
         <v>82</v>
@@ -21953,7 +21959,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21968,7 +21974,7 @@
         <v>102</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>82</v>
@@ -21977,7 +21983,7 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
@@ -21985,10 +21991,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22014,10 +22020,10 @@
         <v>371</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -22068,7 +22074,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -22083,7 +22089,7 @@
         <v>102</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>82</v>
@@ -22092,7 +22098,7 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>82</v>
@@ -22100,10 +22106,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22126,16 +22132,16 @@
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22185,7 +22191,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22200,7 +22206,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -22209,7 +22215,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -22217,13 +22223,13 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>82</v>
@@ -22245,17 +22251,17 @@
         <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
@@ -22304,7 +22310,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -22319,16 +22325,16 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -22336,10 +22342,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22451,10 +22457,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22568,10 +22574,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22597,16 +22603,16 @@
         <v>173</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22616,7 +22622,7 @@
         <v>82</v>
       </c>
       <c r="S163" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="T163" t="s" s="2">
         <v>82</v>
@@ -22634,10 +22640,10 @@
         <v>241</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22655,7 +22661,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22670,7 +22676,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>82</v>
@@ -22687,10 +22693,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22713,19 +22719,19 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22735,7 +22741,7 @@
         <v>82</v>
       </c>
       <c r="S164" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="T164" t="s" s="2">
         <v>82</v>
@@ -22753,10 +22759,10 @@
         <v>155</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22774,7 +22780,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22789,7 +22795,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>82</v>
@@ -22798,7 +22804,7 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22806,10 +22812,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22835,16 +22841,16 @@
         <v>132</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22854,10 +22860,10 @@
         <v>82</v>
       </c>
       <c r="S165" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="T165" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U165" t="s" s="2">
         <v>82</v>
@@ -22893,7 +22899,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22908,7 +22914,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>82</v>
@@ -22917,7 +22923,7 @@
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22925,10 +22931,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22954,13 +22960,13 @@
         <v>104</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22974,7 +22980,7 @@
         <v>82</v>
       </c>
       <c r="T166" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U166" t="s" s="2">
         <v>82</v>
@@ -23010,7 +23016,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -23025,7 +23031,7 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>82</v>
@@ -23034,7 +23040,7 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -23042,10 +23048,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23071,10 +23077,10 @@
         <v>371</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -23125,7 +23131,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -23140,7 +23146,7 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>82</v>
@@ -23149,7 +23155,7 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -23157,10 +23163,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23183,16 +23189,16 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23242,7 +23248,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23257,7 +23263,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>82</v>
@@ -23266,7 +23272,7 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
@@ -23274,13 +23280,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>82</v>
@@ -23302,17 +23308,17 @@
         <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -23361,7 +23367,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23376,16 +23382,16 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
@@ -23393,10 +23399,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23508,10 +23514,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23625,10 +23631,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23654,16 +23660,16 @@
         <v>173</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23673,7 +23679,7 @@
         <v>82</v>
       </c>
       <c r="S172" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="T172" t="s" s="2">
         <v>82</v>
@@ -23691,10 +23697,10 @@
         <v>241</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>82</v>
@@ -23712,7 +23718,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23727,7 +23733,7 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
@@ -23744,10 +23750,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23770,19 +23776,19 @@
         <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -23792,7 +23798,7 @@
         <v>82</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>82</v>
@@ -23810,10 +23816,10 @@
         <v>155</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -23831,7 +23837,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23846,7 +23852,7 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>82</v>
@@ -23855,7 +23861,7 @@
         <v>82</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>82</v>
@@ -23863,10 +23869,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23892,16 +23898,16 @@
         <v>132</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -23911,10 +23917,10 @@
         <v>82</v>
       </c>
       <c r="S174" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="T174" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U174" t="s" s="2">
         <v>82</v>
@@ -23950,7 +23956,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23965,7 +23971,7 @@
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>82</v>
@@ -23974,7 +23980,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23982,10 +23988,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24011,13 +24017,13 @@
         <v>104</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -24031,7 +24037,7 @@
         <v>82</v>
       </c>
       <c r="T175" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U175" t="s" s="2">
         <v>82</v>
@@ -24067,7 +24073,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -24082,7 +24088,7 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>82</v>
@@ -24091,7 +24097,7 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
@@ -24099,10 +24105,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24128,10 +24134,10 @@
         <v>371</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24182,7 +24188,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24197,7 +24203,7 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>82</v>
@@ -24206,7 +24212,7 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -24214,10 +24220,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24240,16 +24246,16 @@
         <v>91</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -24299,7 +24305,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24314,7 +24320,7 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>82</v>
@@ -24323,7 +24329,7 @@
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -24331,13 +24337,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D178" t="s" s="2">
         <v>82</v>
@@ -24359,17 +24365,17 @@
         <v>91</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -24418,7 +24424,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24433,16 +24439,16 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
@@ -24450,10 +24456,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24565,10 +24571,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24682,10 +24688,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24711,16 +24717,16 @@
         <v>173</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24749,7 +24755,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>82</v>
@@ -24767,7 +24773,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24782,7 +24788,7 @@
         <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>82</v>
@@ -24799,10 +24805,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24825,19 +24831,19 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -24847,7 +24853,7 @@
         <v>82</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>82</v>
@@ -24865,10 +24871,10 @@
         <v>155</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>82</v>
@@ -24886,7 +24892,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24901,7 +24907,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>82</v>
@@ -24910,7 +24916,7 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
@@ -24918,10 +24924,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24947,16 +24953,16 @@
         <v>132</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24966,10 +24972,10 @@
         <v>82</v>
       </c>
       <c r="S183" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="T183" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="U183" t="s" s="2">
         <v>82</v>
@@ -25005,7 +25011,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -25020,7 +25026,7 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>82</v>
@@ -25029,7 +25035,7 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -25037,10 +25043,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25066,13 +25072,13 @@
         <v>104</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -25086,7 +25092,7 @@
         <v>82</v>
       </c>
       <c r="T184" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="U184" t="s" s="2">
         <v>82</v>
@@ -25122,7 +25128,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -25137,7 +25143,7 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>82</v>
@@ -25146,7 +25152,7 @@
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
@@ -25154,10 +25160,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25183,10 +25189,10 @@
         <v>371</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -25237,7 +25243,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -25252,7 +25258,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>82</v>
@@ -25261,7 +25267,7 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>82</v>
@@ -25269,10 +25275,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25295,16 +25301,16 @@
         <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -25354,7 +25360,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25369,7 +25375,7 @@
         <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL186" t="s" s="2">
         <v>82</v>
@@ -25378,7 +25384,7 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>82</v>
@@ -25386,10 +25392,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25412,70 +25418,70 @@
         <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q187" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="R187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF187" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q187" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="R187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25490,13 +25496,13 @@
         <v>102</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -25507,10 +25513,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25533,19 +25539,19 @@
         <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
@@ -25582,7 +25588,7 @@
         <v>82</v>
       </c>
       <c r="AB188" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AC188" s="2"/>
       <c r="AD188" t="s" s="2">
@@ -25592,7 +25598,7 @@
         <v>117</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25604,19 +25610,19 @@
         <v>82</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>
@@ -25624,13 +25630,13 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>82</v>
@@ -25652,19 +25658,19 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
@@ -25713,7 +25719,7 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -25725,19 +25731,19 @@
         <v>82</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>82</v>
@@ -25745,10 +25751,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25860,10 +25866,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25977,10 +25983,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26006,16 +26012,16 @@
         <v>173</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -26025,7 +26031,7 @@
         <v>82</v>
       </c>
       <c r="S192" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="T192" t="s" s="2">
         <v>82</v>
@@ -26043,10 +26049,10 @@
         <v>241</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -26064,7 +26070,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -26088,7 +26094,7 @@
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>82</v>
@@ -26096,10 +26102,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26125,13 +26131,13 @@
         <v>104</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="O193" t="s" s="2">
         <v>262</v>
@@ -26183,7 +26189,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -26207,7 +26213,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -26215,14 +26221,14 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -26244,13 +26250,13 @@
         <v>104</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26264,7 +26270,7 @@
         <v>82</v>
       </c>
       <c r="T194" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="U194" t="s" s="2">
         <v>82</v>
@@ -26300,7 +26306,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26315,7 +26321,7 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>82</v>
@@ -26324,7 +26330,7 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>82</v>
@@ -26332,14 +26338,14 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -26361,13 +26367,13 @@
         <v>104</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -26417,7 +26423,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26432,7 +26438,7 @@
         <v>102</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>82</v>
@@ -26441,7 +26447,7 @@
         <v>82</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>82</v>
@@ -26449,10 +26455,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26478,10 +26484,10 @@
         <v>104</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26532,7 +26538,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26547,7 +26553,7 @@
         <v>102</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>82</v>
@@ -26556,7 +26562,7 @@
         <v>82</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
@@ -26564,10 +26570,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26593,10 +26599,10 @@
         <v>104</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26647,7 +26653,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26662,7 +26668,7 @@
         <v>102</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>82</v>
@@ -26671,7 +26677,7 @@
         <v>82</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>
@@ -26679,10 +26685,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26708,14 +26714,14 @@
         <v>371</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>82</v>
@@ -26764,7 +26770,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -26788,7 +26794,7 @@
         <v>82</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>82</v>
@@ -26796,13 +26802,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D199" t="s" s="2">
         <v>82</v>
@@ -26824,19 +26830,19 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>82</v>
@@ -26885,7 +26891,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -26897,19 +26903,19 @@
         <v>82</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -26917,10 +26923,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27032,10 +27038,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27147,13 +27153,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>82</v>
@@ -27175,13 +27181,13 @@
         <v>82</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -27264,10 +27270,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27293,16 +27299,16 @@
         <v>173</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>82</v>
@@ -27312,7 +27318,7 @@
         <v>82</v>
       </c>
       <c r="S203" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>82</v>
@@ -27330,10 +27336,10 @@
         <v>241</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>82</v>
@@ -27351,7 +27357,7 @@
         <v>82</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -27375,7 +27381,7 @@
         <v>82</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>82</v>
@@ -27383,10 +27389,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27412,13 +27418,13 @@
         <v>104</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="O204" t="s" s="2">
         <v>262</v>
@@ -27470,7 +27476,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -27494,7 +27500,7 @@
         <v>82</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>82</v>
@@ -27502,14 +27508,14 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
@@ -27531,13 +27537,13 @@
         <v>104</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27551,7 +27557,7 @@
         <v>82</v>
       </c>
       <c r="T205" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="U205" t="s" s="2">
         <v>82</v>
@@ -27587,7 +27593,7 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -27602,7 +27608,7 @@
         <v>102</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AL205" t="s" s="2">
         <v>82</v>
@@ -27611,7 +27617,7 @@
         <v>82</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>82</v>
@@ -27619,14 +27625,14 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
@@ -27648,13 +27654,13 @@
         <v>104</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -27704,7 +27710,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -27719,7 +27725,7 @@
         <v>102</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AL206" t="s" s="2">
         <v>82</v>
@@ -27728,7 +27734,7 @@
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>82</v>
@@ -27736,10 +27742,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27765,10 +27771,10 @@
         <v>104</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -27819,7 +27825,7 @@
         <v>82</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27834,7 +27840,7 @@
         <v>102</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>82</v>
@@ -27843,7 +27849,7 @@
         <v>82</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>82</v>
@@ -27851,10 +27857,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27880,10 +27886,10 @@
         <v>104</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -27934,7 +27940,7 @@
         <v>82</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -27949,7 +27955,7 @@
         <v>102</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AL208" t="s" s="2">
         <v>82</v>
@@ -27958,7 +27964,7 @@
         <v>82</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>82</v>
@@ -27966,10 +27972,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27995,14 +28001,14 @@
         <v>371</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>82</v>
@@ -28051,7 +28057,7 @@
         <v>82</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -28075,7 +28081,7 @@
         <v>82</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>82</v>
@@ -28083,10 +28089,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28109,19 +28115,19 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>82</v>
@@ -28170,7 +28176,7 @@
         <v>82</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -28185,16 +28191,16 @@
         <v>102</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AM210" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>82</v>
@@ -28202,10 +28208,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28231,16 +28237,16 @@
         <v>173</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>82</v>
@@ -28269,7 +28275,7 @@
       </c>
       <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>82</v>
@@ -28287,7 +28293,7 @@
         <v>82</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -28302,16 +28308,16 @@
         <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="AM211" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>82</v>
@@ -28319,10 +28325,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28345,19 +28351,19 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>82</v>
@@ -28406,7 +28412,7 @@
         <v>82</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -28421,27 +28427,27 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AM212" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28464,19 +28470,19 @@
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>82</v>
@@ -28525,7 +28531,7 @@
         <v>82</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28540,7 +28546,7 @@
         <v>102</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>108</v>
@@ -28549,7 +28555,7 @@
         <v>82</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>82</v>
@@ -28557,10 +28563,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28586,16 +28592,16 @@
         <v>220</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>82</v>
@@ -28644,7 +28650,7 @@
         <v>82</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -28659,16 +28665,16 @@
         <v>102</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>82</v>
@@ -28676,10 +28682,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28702,17 +28708,17 @@
         <v>82</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>82</v>
@@ -28741,7 +28747,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>82</v>
@@ -28759,7 +28765,7 @@
         <v>82</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28774,16 +28780,16 @@
         <v>102</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AM215" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>82</v>
@@ -28791,10 +28797,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28817,19 +28823,19 @@
         <v>82</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>82</v>
@@ -28878,7 +28884,7 @@
         <v>82</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -28893,7 +28899,7 @@
         <v>102</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>108</v>
@@ -28902,7 +28908,7 @@
         <v>82</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>82</v>
@@ -28910,10 +28916,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28936,19 +28942,19 @@
         <v>82</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>82</v>
@@ -28997,7 +29003,7 @@
         <v>82</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -29012,7 +29018,7 @@
         <v>102</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AL217" t="s" s="2">
         <v>108</v>
@@ -29021,7 +29027,7 @@
         <v>82</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>82</v>
@@ -29029,10 +29035,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29055,19 +29061,19 @@
         <v>82</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>82</v>
@@ -29116,7 +29122,7 @@
         <v>82</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -29128,10 +29134,10 @@
         <v>82</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AL218" t="s" s="2">
         <v>108</v>
@@ -29148,10 +29154,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29263,10 +29269,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29376,13 +29382,13 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D221" t="s" s="2">
         <v>82</v>
@@ -29404,13 +29410,13 @@
         <v>82</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -29493,13 +29499,13 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>82</v>
@@ -29521,13 +29527,13 @@
         <v>82</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -29610,14 +29616,14 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
@@ -29639,16 +29645,16 @@
         <v>111</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="N223" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>82</v>
@@ -29697,7 +29703,7 @@
         <v>82</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -29729,10 +29735,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29755,17 +29761,17 @@
         <v>82</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>82</v>
@@ -29793,16 +29799,16 @@
         <v>155</v>
       </c>
       <c r="Y224" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="Z224" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="AC224" s="2"/>
       <c r="AD224" t="s" s="2">
@@ -29812,7 +29818,7 @@
         <v>117</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -29827,7 +29833,7 @@
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>108</v>
@@ -29836,7 +29842,7 @@
         <v>82</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>82</v>
@@ -29844,13 +29850,13 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D225" t="s" s="2">
         <v>82</v>
@@ -29872,17 +29878,17 @@
         <v>82</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>82</v>
@@ -29911,7 +29917,7 @@
       </c>
       <c r="Y225" s="2"/>
       <c r="Z225" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>82</v>
@@ -29929,7 +29935,7 @@
         <v>82</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -29944,7 +29950,7 @@
         <v>102</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="AL225" t="s" s="2">
         <v>108</v>
@@ -29953,7 +29959,7 @@
         <v>82</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>82</v>
@@ -29961,10 +29967,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30076,10 +30082,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30191,13 +30197,13 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>82</v>
@@ -30219,13 +30225,13 @@
         <v>82</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -30308,10 +30314,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30423,10 +30429,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30538,10 +30544,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30581,7 +30587,7 @@
       </c>
       <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="S231" t="s" s="2">
         <v>82</v>
@@ -30655,10 +30661,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30699,7 +30705,7 @@
         <v>82</v>
       </c>
       <c r="S232" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="T232" t="s" s="2">
         <v>82</v>
@@ -30718,7 +30724,7 @@
       </c>
       <c r="Y232" s="2"/>
       <c r="Z232" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>82</v>
@@ -30768,10 +30774,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30797,16 +30803,16 @@
         <v>151</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="O233" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>82</v>
@@ -30855,7 +30861,7 @@
         <v>82</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -30870,7 +30876,7 @@
         <v>102</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>82</v>
@@ -30879,7 +30885,7 @@
         <v>82</v>
       </c>
       <c r="AN233" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="AO233" t="s" s="2">
         <v>82</v>
@@ -30887,10 +30893,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30916,16 +30922,16 @@
         <v>104</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>82</v>
@@ -30974,7 +30980,7 @@
         <v>82</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
@@ -30989,7 +30995,7 @@
         <v>102</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>82</v>
@@ -30998,7 +31004,7 @@
         <v>82</v>
       </c>
       <c r="AN234" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="AO234" t="s" s="2">
         <v>82</v>
@@ -31006,13 +31012,13 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D235" t="s" s="2">
         <v>82</v>
@@ -31034,17 +31040,17 @@
         <v>82</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>82</v>
@@ -31073,7 +31079,7 @@
       </c>
       <c r="Y235" s="2"/>
       <c r="Z235" t="s" s="2">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="AA235" t="s" s="2">
         <v>82</v>
@@ -31091,7 +31097,7 @@
         <v>82</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -31106,7 +31112,7 @@
         <v>102</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="AL235" t="s" s="2">
         <v>108</v>
@@ -31115,7 +31121,7 @@
         <v>82</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>82</v>
@@ -31123,10 +31129,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31238,10 +31244,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31353,13 +31359,13 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>82</v>
@@ -31381,13 +31387,13 @@
         <v>82</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -31470,10 +31476,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31585,10 +31591,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31700,10 +31706,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31743,7 +31749,7 @@
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="S241" t="s" s="2">
         <v>82</v>
@@ -31817,10 +31823,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31861,7 +31867,7 @@
         <v>82</v>
       </c>
       <c r="S242" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="T242" t="s" s="2">
         <v>82</v>
@@ -31880,7 +31886,7 @@
       </c>
       <c r="Y242" s="2"/>
       <c r="Z242" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>82</v>
@@ -31930,10 +31936,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31959,16 +31965,16 @@
         <v>151</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>82</v>
@@ -32017,7 +32023,7 @@
         <v>82</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -32032,7 +32038,7 @@
         <v>102</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="AL243" t="s" s="2">
         <v>82</v>
@@ -32041,7 +32047,7 @@
         <v>82</v>
       </c>
       <c r="AN243" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="AO243" t="s" s="2">
         <v>82</v>
@@ -32049,10 +32055,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -32078,16 +32084,16 @@
         <v>104</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="O244" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>82</v>
@@ -32136,7 +32142,7 @@
         <v>82</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
@@ -32151,7 +32157,7 @@
         <v>102</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="AL244" t="s" s="2">
         <v>82</v>
@@ -32160,7 +32166,7 @@
         <v>82</v>
       </c>
       <c r="AN244" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="AO244" t="s" s="2">
         <v>82</v>
@@ -32168,10 +32174,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -32194,17 +32200,17 @@
         <v>82</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" t="s" s="2">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="P245" t="s" s="2">
         <v>82</v>
@@ -32253,7 +32259,7 @@
         <v>82</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>80</v>
@@ -32268,7 +32274,7 @@
         <v>102</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AL245" t="s" s="2">
         <v>108</v>
@@ -32277,7 +32283,7 @@
         <v>82</v>
       </c>
       <c r="AN245" t="s" s="2">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AO245" t="s" s="2">
         <v>82</v>
@@ -32285,10 +32291,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -32311,19 +32317,19 @@
         <v>82</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>82</v>
@@ -32372,7 +32378,7 @@
         <v>82</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>80</v>
@@ -32387,7 +32393,7 @@
         <v>102</v>
       </c>
       <c r="AK246" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AL246" t="s" s="2">
         <v>108</v>
@@ -32396,7 +32402,7 @@
         <v>82</v>
       </c>
       <c r="AN246" t="s" s="2">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="AO246" t="s" s="2">
         <v>82</v>
@@ -32404,10 +32410,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32430,17 +32436,17 @@
         <v>82</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="P247" t="s" s="2">
         <v>82</v>
@@ -32489,7 +32495,7 @@
         <v>82</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>80</v>
@@ -32504,7 +32510,7 @@
         <v>102</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="AL247" t="s" s="2">
         <v>108</v>
@@ -32513,7 +32519,7 @@
         <v>82</v>
       </c>
       <c r="AN247" t="s" s="2">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="AO247" t="s" s="2">
         <v>82</v>
@@ -32521,10 +32527,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32550,14 +32556,14 @@
         <v>173</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>82</v>
@@ -32585,10 +32591,10 @@
         <v>241</v>
       </c>
       <c r="Y248" t="s" s="2">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="Z248" t="s" s="2">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="AA248" t="s" s="2">
         <v>82</v>
@@ -32606,7 +32612,7 @@
         <v>82</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>80</v>
@@ -32621,7 +32627,7 @@
         <v>102</v>
       </c>
       <c r="AK248" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AL248" t="s" s="2">
         <v>108</v>
@@ -32630,7 +32636,7 @@
         <v>82</v>
       </c>
       <c r="AN248" t="s" s="2">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="AO248" t="s" s="2">
         <v>82</v>
@@ -32638,10 +32644,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32664,17 +32670,17 @@
         <v>82</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" t="s" s="2">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="P249" t="s" s="2">
         <v>82</v>
@@ -32723,7 +32729,7 @@
         <v>82</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>80</v>
@@ -32732,13 +32738,13 @@
         <v>90</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK249" t="s" s="2">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="AL249" t="s" s="2">
         <v>108</v>
@@ -32747,7 +32753,7 @@
         <v>82</v>
       </c>
       <c r="AN249" t="s" s="2">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="AO249" t="s" s="2">
         <v>82</v>
@@ -32755,10 +32761,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32784,10 +32790,10 @@
         <v>371</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
@@ -32838,7 +32844,7 @@
         <v>82</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>80</v>
@@ -32853,7 +32859,7 @@
         <v>102</v>
       </c>
       <c r="AK250" t="s" s="2">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="AL250" t="s" s="2">
         <v>108</v>
@@ -32870,10 +32876,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32896,19 +32902,19 @@
         <v>82</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="N251" t="s" s="2">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="O251" t="s" s="2">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="P251" t="s" s="2">
         <v>82</v>
@@ -32957,7 +32963,7 @@
         <v>82</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>80</v>
@@ -32972,10 +32978,10 @@
         <v>102</v>
       </c>
       <c r="AK251" t="s" s="2">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="AL251" t="s" s="2">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="AM251" t="s" s="2">
         <v>82</v>
@@ -32989,10 +32995,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -33104,10 +33110,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -33221,14 +33227,14 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E254" s="2"/>
       <c r="F254" t="s" s="2">
@@ -33250,16 +33256,16 @@
         <v>111</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="N254" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O254" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P254" t="s" s="2">
         <v>82</v>
@@ -33308,7 +33314,7 @@
         <v>82</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
@@ -33340,10 +33346,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -33366,19 +33372,19 @@
         <v>82</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="N255" t="s" s="2">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="O255" t="s" s="2">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>82</v>
@@ -33427,7 +33433,7 @@
         <v>82</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>90</v>
@@ -33442,16 +33448,16 @@
         <v>102</v>
       </c>
       <c r="AK255" t="s" s="2">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="AM255" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN255" t="s" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="AO255" t="s" s="2">
         <v>82</v>
@@ -33459,10 +33465,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -33485,19 +33491,19 @@
         <v>82</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="O256" t="s" s="2">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="P256" t="s" s="2">
         <v>82</v>
@@ -33546,7 +33552,7 @@
         <v>82</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>80</v>
@@ -33561,16 +33567,16 @@
         <v>102</v>
       </c>
       <c r="AK256" t="s" s="2">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="AM256" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN256" t="s" s="2">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="AO256" t="s" s="2">
         <v>82</v>
@@ -33578,14 +33584,14 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
@@ -33604,16 +33610,16 @@
         <v>82</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
@@ -33663,7 +33669,7 @@
         <v>82</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>80</v>
@@ -33678,7 +33684,7 @@
         <v>102</v>
       </c>
       <c r="AK257" t="s" s="2">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="AL257" t="s" s="2">
         <v>108</v>
@@ -33687,7 +33693,7 @@
         <v>82</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>82</v>
@@ -33695,10 +33701,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33721,19 +33727,19 @@
         <v>91</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="O258" t="s" s="2">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>82</v>
@@ -33782,7 +33788,7 @@
         <v>82</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>80</v>
@@ -33797,10 +33803,10 @@
         <v>102</v>
       </c>
       <c r="AK258" t="s" s="2">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="AM258" t="s" s="2">
         <v>82</v>
@@ -33814,10 +33820,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33840,19 +33846,19 @@
         <v>91</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="O259" t="s" s="2">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="P259" t="s" s="2">
         <v>82</v>
@@ -33901,7 +33907,7 @@
         <v>82</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>80</v>
@@ -33916,7 +33922,7 @@
         <v>102</v>
       </c>
       <c r="AK259" t="s" s="2">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="AL259" t="s" s="2">
         <v>108</v>
@@ -33933,10 +33939,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -34048,10 +34054,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -34165,14 +34171,14 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
@@ -34194,16 +34200,16 @@
         <v>111</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="N262" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O262" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P262" t="s" s="2">
         <v>82</v>
@@ -34252,7 +34258,7 @@
         <v>82</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>80</v>
@@ -34284,10 +34290,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -34310,16 +34316,16 @@
         <v>91</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
@@ -34369,7 +34375,7 @@
         <v>82</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>90</v>
@@ -34384,7 +34390,7 @@
         <v>102</v>
       </c>
       <c r="AK263" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL263" t="s" s="2">
         <v>108</v>
@@ -34393,7 +34399,7 @@
         <v>82</v>
       </c>
       <c r="AN263" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="AO263" t="s" s="2">
         <v>82</v>
@@ -34401,10 +34407,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -34430,10 +34436,10 @@
         <v>173</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34463,28 +34469,28 @@
         <v>241</v>
       </c>
       <c r="Y264" t="s" s="2">
+        <v>1047</v>
+      </c>
+      <c r="Z264" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="AA264" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB264" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC264" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD264" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE264" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF264" t="s" s="2">
         <v>1045</v>
-      </c>
-      <c r="Z264" t="s" s="2">
-        <v>1046</v>
-      </c>
-      <c r="AA264" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB264" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC264" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD264" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE264" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF264" t="s" s="2">
-        <v>1043</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>90</v>
@@ -34499,7 +34505,7 @@
         <v>102</v>
       </c>
       <c r="AK264" t="s" s="2">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="AL264" t="s" s="2">
         <v>108</v>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1311,8 +1311,8 @@
     <t>FR Core Patient Identity Reliability Extension</t>
   </si>
   <si>
-    <t>Extension composite précisant le degré de confiance de l'identité du patient au sens du Référentiel National d'Identitovigilance (RNIV) : statut de confiance (provisoire, récupérée, validée, qualifiée), canal d'obtention des traits d'identité ou de l'INS, pièce justificative contrôlée, dates associées et annotations complémentaires.
-Composite extension specifying the confidence level of a patient's identity per the French National Identity Vigilance Framework (RNIV): trust status (provisional, recovered, validated, qualified), channel used to collect the identity traits or the INS, validation evidence, related dates and additional annotations.</t>
+    <t>Extension composite précisant le degré de confiance de l'identité du patient au sens du Référentiel National d'Identitovigilance (RNIV) : statut de confiance (provisoire, récupérée, validée, qualifiée), canal d'obtention des traits d'identité ou du matricule INS, pièce justificative contrôlée, dates associées et annotations complémentaires.
+Composite extension specifying the confidence level of a patient's identity per the French National Identity Vigilance Framework (RNIV): trust status (provisional, recovered, validated, qualified), channel used to collect the identity traits or the INS identifier, validation evidence, related dates and additional annotations.</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.id</t>
@@ -1327,10 +1327,10 @@
     <t>methodCollection</t>
   </si>
   <si>
-    <t>Canal d'obtention des traits d'identité ou de l'INS (SM, CV, INSi, CB, RFID, AV) | Channel used to collect the identity traits or the INS</t>
-  </si>
-  <si>
-    <t>Précise le canal par lequel les traits d'identité ou l'INS ont été obtenus : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>
+    <t>Canal d'obtention des traits d'identité ou du matricule INS (SM, CV, INSi, CB, RFID, AV) | Channel used to collect the identity traits or the INS identifier</t>
+  </si>
+  <si>
+    <t>Précise le canal par lequel les traits d'identité ou le matricule INS ont été obtenus : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID ou Application carte Vitale. Ce champ ne porte pas le statut de confiance résultant (cf. sous-extension `identityStatus`) ni la pièce justificative contrôlée (cf. sous-extension `validationMode`).</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:methodCollection.id</t>
@@ -1369,10 +1369,10 @@
     <t>dateCollection</t>
   </si>
   <si>
-    <t>Date d'obtention des traits d'identité ou de l'INS | Date the identity traits or the INS were collected</t>
-  </si>
-  <si>
-    <t>Date à laquelle les traits d'identité ou l'INS ont été obtenus, quel que soit le canal utilisé (cf. sous-extension `methodCollection`) : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID. Cette date ne doit pas être confondue avec la date de vérification de l'identité (cf. sous-extension `validationDate`). | Date at which the identity traits or the INS were obtained, regardless of the channel used (see the `methodCollection` sub-extension): manual entry, Vitale card reading, direct query of the INSi teleservice, barcode/Datamatrix scan, RFID reading. This date must not be confused with the identity verification date (see the `validationDate` sub-extension).</t>
+    <t>Date d'obtention des traits d'identité ou du matricule INS | Date the identity traits or the INS identifier were collected</t>
+  </si>
+  <si>
+    <t>Date à laquelle les traits d'identité ou le matricule INS ont été obtenus, quel que soit le canal utilisé (cf. sous-extension `methodCollection`) : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID. Cette date ne doit pas être confondue avec la date de vérification de l'identité (cf. sous-extension `validationDate`). | Date at which the identity traits or the INS identifier were obtained, regardless of the channel used (see the `methodCollection` sub-extension): manual entry, Vitale card reading, direct query of the INSi teleservice, barcode/Datamatrix scan, RFID reading. This date must not be confused with the identity verification date (see the `validationDate` sub-extension).</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability.extension:dateCollection.id</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1363,28 +1363,28 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-identity-method-collection|2.2.0</t>
   </si>
   <si>
-    <t>Patient.extension:identityReliability.extension:dateCollection</t>
-  </si>
-  <si>
-    <t>dateCollection</t>
-  </si>
-  <si>
-    <t>Date d'obtention des traits d'identité ou du matricule INS | Date the identity traits or the INS identifier were collected</t>
-  </si>
-  <si>
-    <t>Date à laquelle les traits d'identité ou le matricule INS ont été obtenus, quel que soit le canal utilisé (cf. sous-extension `methodCollection`) : saisie manuelle, lecture de la carte Vitale, interrogation directe du téléservice INSi, scan d'un code à barre/Datamatrix, lecture RFID. Cette date ne doit pas être confondue avec la date de vérification de l'identité (cf. sous-extension `validationDate`). | Date at which the identity traits or the INS identifier were obtained, regardless of the channel used (see the `methodCollection` sub-extension): manual entry, Vitale card reading, direct query of the INSi teleservice, barcode/Datamatrix scan, RFID reading. This date must not be confused with the identity verification date (see the `validationDate` sub-extension).</t>
-  </si>
-  <si>
-    <t>Patient.extension:identityReliability.extension:dateCollection.id</t>
-  </si>
-  <si>
-    <t>Patient.extension:identityReliability.extension:dateCollection.extension</t>
-  </si>
-  <si>
-    <t>Patient.extension:identityReliability.extension:dateCollection.url</t>
-  </si>
-  <si>
-    <t>Patient.extension:identityReliability.extension:dateCollection.value[x]</t>
+    <t>Patient.extension:identityReliability.extension:dateInterrogationINSi</t>
+  </si>
+  <si>
+    <t>dateInterrogationINSi</t>
+  </si>
+  <si>
+    <t>Date d'interrogation du téléservice INSi | Date the INSi teleservice was queried</t>
+  </si>
+  <si>
+    <t>Date à laquelle le téléservice INSi a été appelé. Ce champ est renseigné chaque fois que le téléservice INSi est interrogé, que ce soit par lecture de la carte Vitale ou par saisie directe des traits d'identité (cf. sous-extension `methodCollection`), à l'exception des usagers de l'Application carte Vitale et de leurs ayants droit, pour lesquels le RNIV exclut explicitement l'appel au téléservice. Cette date ne doit pas être confondue avec la date de vérification de l'identité (cf. sous-extension `validationDate`). | Date at which the INSi teleservice was queried. This field is populated whenever the INSi teleservice is queried, whether via Vitale card reading or direct entry of identity traits (see the `methodCollection` sub-extension), except for Appli carte Vitale users and their dependents, for whom the RNIV explicitly excludes the teleservice call. This date must not be confused with the identity verification date (see the `validationDate` sub-extension).</t>
+  </si>
+  <si>
+    <t>Patient.extension:identityReliability.extension:dateInterrogationINSi.id</t>
+  </si>
+  <si>
+    <t>Patient.extension:identityReliability.extension:dateInterrogationINSi.extension</t>
+  </si>
+  <si>
+    <t>Patient.extension:identityReliability.extension:dateInterrogationINSi.url</t>
+  </si>
+  <si>
+    <t>Patient.extension:identityReliability.extension:dateInterrogationINSi.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">date

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
